--- a/AAII_Financials/Quarterly/ARM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="92">
   <si>
     <t>ARM</t>
   </si>
@@ -656,216 +656,223 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1289000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1490000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1242000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1135000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1053000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1241000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>983000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>844000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>939000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>928000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>824000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>806000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>675000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>633000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>724000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>630000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>692000</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>36000</v>
+      </c>
+      <c r="E9" s="3">
         <v>32000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>30000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>29000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>30000</v>
-      </c>
-      <c r="H9" s="3">
-        <v>28000</v>
       </c>
       <c r="I9" s="3">
         <v>28000</v>
       </c>
       <c r="J9" s="3">
+        <v>28000</v>
+      </c>
+      <c r="K9" s="3">
         <v>32000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>33000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>41000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>36000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>46000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>31000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>27000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>29000</v>
-      </c>
-      <c r="R9" s="3">
-        <v>25000</v>
       </c>
       <c r="S9" s="3">
         <v>25000</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
+      <c r="T9" s="3">
+        <v>25000</v>
       </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
@@ -873,70 +880,76 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1253000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1458000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1212000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1106000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1023000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1213000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>955000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>812000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>906000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>887000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>788000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>760000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>644000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>606000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>695000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>605000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>667000</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -959,70 +972,74 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>838000</v>
+      </c>
+      <c r="E12" s="3">
         <v>698000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>737000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>691000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>650000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>546000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>533000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>507000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>485000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>584000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>432000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>626000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>337000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>381000</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S12" s="3">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T12" s="3">
         <v>218000</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1083,20 +1100,23 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E14" s="3">
         <v>2000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>6000</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1112,86 +1132,89 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>-500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>6000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-40000</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
         <v>35500</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T14" s="3">
         <v>2000</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>75000</v>
+      </c>
+      <c r="E15" s="3">
         <v>71000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>63000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>55000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>60000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>27800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>47000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>44000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>43000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>23500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>42000</v>
-      </c>
-      <c r="N15" s="3">
-        <v>41000</v>
       </c>
       <c r="O15" s="3">
         <v>41000</v>
       </c>
       <c r="P15" s="3">
+        <v>41000</v>
+      </c>
+      <c r="Q15" s="3">
         <v>17500</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1207,8 +1230,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1228,132 +1254,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1191000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1050000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1051000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>972000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>939000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>831000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>808000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>780000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>757000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>906500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>684000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1002000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>564000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>647500</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S17" s="3">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T17" s="3">
         <v>398000</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>98000</v>
+      </c>
+      <c r="E18" s="3">
         <v>440000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>191000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>163000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>114000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>410000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>175000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>64000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>182000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>21500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>140000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-196000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>111000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-14500</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T18" s="3">
         <v>294000</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1376,132 +1409,139 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-131000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-15000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-14000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-112000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-5000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>293000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-65000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>29000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-30000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-6000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>16000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-9000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>8000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-34000</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S20" s="3">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T20" s="3">
         <v>-8000</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>304000</v>
+      </c>
+      <c r="E21" s="3">
         <v>526000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>268000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>330000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>179000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>144800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>287000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>79000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>255000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>51000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>166000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-146000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>144000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>37000</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3">
         <v>328000</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1544,8 +1584,8 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1562,132 +1602,141 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>253000</v>
+      </c>
+      <c r="E23" s="3">
         <v>481000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>228000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>302000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>146000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>144000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>268000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>64000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>244000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>58000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>146000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-119000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>127000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>5000</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S23" s="3">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T23" s="3">
         <v>286000</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="E24" s="3">
         <v>168000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>64000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>16000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-66000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>16000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-43000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>21000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-166000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>59000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-9000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>22000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2000</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S24" s="3">
+      <c r="S24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T24" s="3">
         <v>61000</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1748,132 +1797,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>270000</v>
+      </c>
+      <c r="E26" s="3">
         <v>313000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>223000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>238000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>130000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>210000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>252000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>107000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>223000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>224000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>87000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-110000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>105000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3000</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S26" s="3">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T26" s="3">
         <v>225000</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>270000</v>
+      </c>
+      <c r="E27" s="3">
         <v>313000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>223000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>238000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>130000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>210000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>252000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>107000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>223000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>224000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>87000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-110000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>105000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3000</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S27" s="3">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T27" s="3">
         <v>225000</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1934,8 +1992,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1996,8 +2057,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2058,8 +2122,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2120,132 +2187,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>131000</v>
+      </c>
+      <c r="E32" s="3">
         <v>15000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>14000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>112000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>5000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-293000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>65000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-29000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>30000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>6000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-16000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>9000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-8000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>34000</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S32" s="3">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T32" s="3">
         <v>8000</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>270000</v>
+      </c>
+      <c r="E33" s="3">
         <v>313000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>223000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>238000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>130000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>210000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>252000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>107000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>223000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>224000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>87000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-110000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>105000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3000</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S33" s="3">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T33" s="3">
         <v>225000</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2306,137 +2382,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>270000</v>
+      </c>
+      <c r="E35" s="3">
         <v>313000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>223000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>238000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>130000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>210000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>252000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>107000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>223000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>224000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>87000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-110000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>105000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3000</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S35" s="3">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T35" s="3">
         <v>225000</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2459,8 +2544,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2483,53 +2569,54 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3058000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2751000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2807000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2518000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1956000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2085000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2036000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1498000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1465000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1923000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1551000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1406000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1248000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1554000</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2545,53 +2632,56 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>830000</v>
+      </c>
+      <c r="E42" s="3">
         <v>850000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>735000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>740000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>950000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>740000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>635000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>860000</v>
-      </c>
-      <c r="K42" s="3">
-        <v>1000000</v>
       </c>
       <c r="L42" s="3">
         <v>1000000</v>
       </c>
       <c r="M42" s="3">
+        <v>1000000</v>
+      </c>
+      <c r="N42" s="3">
         <v>850000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>800000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>801000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>661000</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2607,53 +2697,56 @@
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2223000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2466000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2011000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1976000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2152000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1898000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1592000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1635000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1259000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1225000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1079000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1099000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1067000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1165000</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2669,8 +2762,11 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2713,8 +2809,8 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -2731,8 +2827,11 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2763,20 +2862,20 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>10000</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O45" s="3">
-        <v>10000</v>
+      <c r="O45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P45" s="3">
         <v>10000</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
+      <c r="Q45" s="3">
+        <v>10000</v>
       </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
@@ -2793,53 +2892,56 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6339000</v>
+      </c>
+      <c r="E46" s="3">
         <v>6236000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5736000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5370000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5173000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4830000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4334000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4064000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3840000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4197000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3628000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3442000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3237000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3537000</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2855,53 +2957,56 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>606800</v>
+      </c>
+      <c r="E47" s="3">
         <v>387000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>369000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>556000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>570000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>565000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>845000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>796000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>800000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>741000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>748000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>725000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>727000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>723000</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2917,53 +3022,56 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1391000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1220000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1189000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1014000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>873000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>714000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>599000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>523000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>464000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>420000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>425000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>410000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>403000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>391000</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2979,53 +3087,56 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1840000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1853000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1865000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1870000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1889000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1771000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1781000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1825000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1784000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1777000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1791000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1762000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1795000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1758000</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3041,8 +3152,11 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3103,8 +3217,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3165,53 +3282,56 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>228200</v>
+      </c>
+      <c r="E52" s="3">
         <v>312000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>300000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>214500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>210800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>271200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>231700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>213500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>272300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>237600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>208000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>179400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>216700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>171100</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3227,8 +3347,11 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3289,53 +3412,56 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>11196000</v>
+      </c>
+      <c r="E54" s="3">
         <v>10703000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10176000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9710000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9395000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8932000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8496000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8086000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7880000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7927000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7115000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6810000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6700000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6866000</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3351,8 +3477,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3375,8 +3504,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3399,55 +3529,56 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>52000</v>
+      </c>
+      <c r="E57" s="3">
         <v>80000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>78000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>67000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>71000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>63000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>70000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>34000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>46000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>26000</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P57" s="3">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3">
         <v>82000</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R57" s="3">
-        <v>0</v>
+      <c r="R57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S57" s="3">
         <v>0</v>
@@ -3461,61 +3592,64 @@
       <c r="V57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>64000</v>
+        <v>62000</v>
       </c>
       <c r="E58" s="3">
         <v>64000</v>
       </c>
       <c r="F58" s="3">
+        <v>64000</v>
+      </c>
+      <c r="G58" s="3">
         <v>56000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>57000</v>
-      </c>
-      <c r="H58" s="3">
-        <v>40000</v>
       </c>
       <c r="I58" s="3">
         <v>40000</v>
       </c>
       <c r="J58" s="3">
+        <v>40000</v>
+      </c>
+      <c r="K58" s="3">
         <v>34000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>33000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>32000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>26000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>24000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>26000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>28000</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
-      </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T58" s="3">
+        <v>0</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
@@ -3523,53 +3657,56 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>370000</v>
+      </c>
+      <c r="E59" s="3">
         <v>478000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>515000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>464000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>420000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>387000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>383000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>430000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>452000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>392000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>629000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>612000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>786000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>497000</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3585,53 +3722,56 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1207000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1040000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1057000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>960000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1037000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>929000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>874000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>899000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1065000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1505000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>866000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>795000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>946000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1363000</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3647,53 +3787,56 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>423000</v>
+      </c>
+      <c r="E61" s="3">
         <v>427000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>397000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>373000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>339000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>331000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>231000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>229000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>221000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>194000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>195000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>190000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>197000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>193000</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3709,53 +3852,56 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>174000</v>
+      </c>
+      <c r="E62" s="3">
         <v>159000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>198000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>209000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>215000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>90000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>99000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>111000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>74000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>81000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>79000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>71000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>296000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>190000</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3771,8 +3917,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3833,8 +3982,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3895,8 +4047,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3957,53 +4112,56 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2566000</v>
+      </c>
+      <c r="E66" s="3">
         <v>2417000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2378000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2303000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2388000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2093000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2077000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2074000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2217000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2632000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2111000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2037000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2479000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2815000</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4019,8 +4177,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4043,8 +4204,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4105,8 +4267,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4167,8 +4332,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4229,8 +4397,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4291,53 +4462,56 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4717000</v>
+      </c>
+      <c r="E72" s="3">
         <v>4447000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>4134000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3911000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3673000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3543000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3333000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3081000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2974000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2751000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2527000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2440000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2562000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2457000</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4353,8 +4527,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4415,8 +4592,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4477,8 +4657,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4539,53 +4722,56 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8630000</v>
+      </c>
+      <c r="E76" s="3">
         <v>8286000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7798000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7407000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7007000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6839000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6419000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6012000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5663000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5295000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5004000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4773000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4221000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4051000</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4601,8 +4787,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4663,137 +4852,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>270000</v>
+      </c>
+      <c r="E81" s="3">
         <v>313000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>223000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>238000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>130000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>210000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>252000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>107000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>223000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>224000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>87000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-110000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>105000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3000</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S81" s="3">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T81" s="3">
         <v>225000</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4816,50 +5014,51 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>36000</v>
+      </c>
+      <c r="E83" s="3">
         <v>-30800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>47000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>44000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>20000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>23500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>42000</v>
-      </c>
-      <c r="J83" s="3">
-        <v>41000</v>
       </c>
       <c r="K83" s="3">
         <v>41000</v>
       </c>
       <c r="L83" s="3">
+        <v>41000</v>
+      </c>
+      <c r="M83" s="3">
         <v>17500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>43000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>45000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>42000</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4878,8 +5077,11 @@
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4940,8 +5142,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5002,8 +5207,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5064,8 +5272,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5126,8 +5337,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5188,53 +5402,56 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>902000</v>
+      </c>
+      <c r="E89" s="3">
         <v>260000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>365000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>567000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>332000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>258000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>423000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>6000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-290000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>667000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>310000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>227000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-114000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>483000</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5250,8 +5467,11 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5274,53 +5494,54 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-197000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-74000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-179000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-138000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-154000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-74000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-63000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-53000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-29000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-11000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-21000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-34000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-26000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-16000</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
@@ -5336,8 +5557,11 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5398,8 +5622,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5460,53 +5687,56 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-267000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-201000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>52000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>196000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-372000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-188000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>152000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>75000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-74000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-170000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-123000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-46000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-177000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-21000</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5522,8 +5752,11 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5546,8 +5779,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5590,8 +5824,8 @@
       <c r="P96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -5608,8 +5842,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5670,8 +5907,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5732,8 +5972,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5794,53 +6037,56 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-326000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-105000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-130000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-190000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-123000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-27000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-26000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-53000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-96000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-121000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-48000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-24000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-15000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-10000</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5856,50 +6102,53 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>34000</v>
+      </c>
+      <c r="E101" s="3">
         <v>6000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-11000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>5000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-4000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>6000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1000</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L101" s="3">
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3">
         <v>1000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>11000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-11000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-10000</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5909,8 +6158,8 @@
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
+      <c r="T101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U101" s="3">
         <v>0</v>
@@ -5918,53 +6167,56 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>307000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-56000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>289000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>562000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-129000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>49000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>538000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>33000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-458000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>372000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>145000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>158000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-306000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>453000</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5978,6 +6230,9 @@
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
